--- a/Deliverables/BOM/LCSC_BOM.xlsx
+++ b/Deliverables/BOM/LCSC_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ezlo-thermostat\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1029511-B856-4CED-90C5-F26CC188BD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0429A40-4B9C-4459-B69C-ED6D30182405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>#</t>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t>C109447</t>
-  </si>
-  <si>
-    <t>C326057</t>
   </si>
   <si>
     <t>C315248</t>
@@ -245,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -275,6 +272,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -563,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C0EAC8-2749-4D8B-AD6B-98E76B44D0B5}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -587,10 +596,10 @@
       <c r="A3" s="9">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="14">
         <v>100</v>
       </c>
     </row>
@@ -598,10 +607,10 @@
       <c r="A4" s="9">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="12">
         <v>100</v>
       </c>
     </row>
@@ -609,87 +618,76 @@
       <c r="A5" s="9">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="14">
         <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6" t="s">
+      <c r="A6" s="10">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2">
         <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
-        <v>5</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="1">
-        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="2">
-        <v>20</v>
+      <c r="C8" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="A9" s="10">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
-        <v>8</v>
-      </c>
-      <c r="B10" s="6" t="s">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="2">
-        <v>100</v>
+      <c r="C10" s="1">
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
-        <v>9</v>
-      </c>
-      <c r="B11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="1">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9">
-        <v>10</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="8">
+      <c r="C11" s="8">
         <v>50</v>
       </c>
     </row>
